--- a/agent_runs/manjidiwang/episodes/ep14/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep14/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>新债提案压上会议桌（，总时长：13秒，镜头数：3个）</t>
+          <t>新债提案压上会议桌</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>朱天和拍桌反对（，总时长：11秒，镜头数：4个）</t>
+          <t>朱天和拍桌反对</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>多数举手通过新债（，总时长：10秒，镜头数：4个）</t>
+          <t>多数举手通过新债</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>黑锅与反钩（，总时长：10秒，镜头数：5个）</t>
+          <t>黑锅与反钩</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>残缺数据露出转账痕迹（，总时长：10秒，镜头数：4个）</t>
+          <t>残缺数据露出转账痕迹</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>红星账户与龙字浮现（，总时长：12秒，镜头数：5个）</t>
+          <t>红星账户与龙字浮现</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>鼎丰资本浮出水面（，总时长：15秒，镜头数：5个）</t>
+          <t>鼎丰资本浮出水面</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>十二暗股指向幕后人（，总时长：11秒，镜头数：4个）</t>
+          <t>十二暗股指向幕后人</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>实地调查前带上防身物（，总时长：11秒，镜头数：5个）</t>
+          <t>实地调查前带上防身物</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
